--- a/vignettes/vignette-2/distribution_stats.xlsx
+++ b/vignettes/vignette-2/distribution_stats.xlsx
@@ -496,22 +496,22 @@
         <v>491</v>
       </c>
       <c r="C3" t="n">
-        <v>245</v>
+        <v>285</v>
       </c>
       <c r="D3" t="n">
-        <v>-8.500000000000001e-05</v>
+        <v>0.019249</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07829700000000001</v>
+        <v>0.101941</v>
       </c>
       <c r="F3" t="n">
-        <v>0.024145</v>
+        <v>0.047935</v>
       </c>
       <c r="G3" t="n">
-        <v>0.16703</v>
+        <v>0.362579</v>
       </c>
       <c r="H3" t="n">
-        <v>0.280076</v>
+        <v>0.559982</v>
       </c>
     </row>
     <row r="4">
@@ -524,22 +524,22 @@
         <v>491</v>
       </c>
       <c r="C4" t="n">
-        <v>249</v>
+        <v>285</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.000481</v>
+        <v>0.020755</v>
       </c>
       <c r="E4" t="n">
-        <v>0.09223199999999999</v>
+        <v>0.109915</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02694</v>
+        <v>0.051686</v>
       </c>
       <c r="G4" t="n">
-        <v>0.183428</v>
+        <v>0.390944</v>
       </c>
       <c r="H4" t="n">
-        <v>0.303457</v>
+        <v>0.603789</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>-0.000396</v>
+        <v>0.001506</v>
       </c>
       <c r="E5" t="n">
-        <v>0.013935</v>
+        <v>0.007974</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002795</v>
+        <v>0.003751</v>
       </c>
       <c r="G5" t="n">
-        <v>0.016398</v>
+        <v>0.028365</v>
       </c>
       <c r="H5" t="n">
-        <v>0.023381</v>
+        <v>0.043807</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/distribution_stats.xlsx
+++ b/vignettes/vignette-2/distribution_stats.xlsx
@@ -465,25 +465,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>491</v>
+        <v>789</v>
       </c>
       <c r="C2" t="n">
-        <v>285</v>
+        <v>453</v>
       </c>
       <c r="D2" t="n">
-        <v>0.021265</v>
+        <v>0.024278</v>
       </c>
       <c r="E2" t="n">
-        <v>0.138908</v>
+        <v>0.180225</v>
       </c>
       <c r="F2" t="n">
-        <v>0.061269</v>
+        <v>0.067604</v>
       </c>
       <c r="G2" t="n">
-        <v>0.563588</v>
+        <v>0.766636</v>
       </c>
       <c r="H2" t="n">
-        <v>0.717422</v>
+        <v>0.864212</v>
       </c>
     </row>
     <row r="3">
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>491</v>
+        <v>789</v>
       </c>
       <c r="C3" t="n">
-        <v>285</v>
+        <v>453</v>
       </c>
       <c r="D3" t="n">
-        <v>0.019249</v>
+        <v>0.020263</v>
       </c>
       <c r="E3" t="n">
-        <v>0.101941</v>
+        <v>0.109771</v>
       </c>
       <c r="F3" t="n">
-        <v>0.047935</v>
+        <v>0.054537</v>
       </c>
       <c r="G3" t="n">
-        <v>0.362579</v>
+        <v>0.370035</v>
       </c>
       <c r="H3" t="n">
-        <v>0.559982</v>
+        <v>0.592711</v>
       </c>
     </row>
     <row r="4">
@@ -521,25 +521,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>491</v>
+        <v>789</v>
       </c>
       <c r="C4" t="n">
-        <v>285</v>
+        <v>453</v>
       </c>
       <c r="D4" t="n">
-        <v>0.020755</v>
+        <v>0.022021</v>
       </c>
       <c r="E4" t="n">
-        <v>0.109915</v>
+        <v>0.1193</v>
       </c>
       <c r="F4" t="n">
-        <v>0.051686</v>
+        <v>0.059271</v>
       </c>
       <c r="G4" t="n">
-        <v>0.390944</v>
+        <v>0.402157</v>
       </c>
       <c r="H4" t="n">
-        <v>0.603789</v>
+        <v>0.644163</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.001506</v>
+        <v>0.001758</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007974</v>
+        <v>0.009528999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003751</v>
+        <v>0.004734</v>
       </c>
       <c r="G5" t="n">
-        <v>0.028365</v>
+        <v>0.032122</v>
       </c>
       <c r="H5" t="n">
-        <v>0.043807</v>
+        <v>0.051452</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/distribution_stats.xlsx
+++ b/vignettes/vignette-2/distribution_stats.xlsx
@@ -499,19 +499,19 @@
         <v>453</v>
       </c>
       <c r="D3" t="n">
-        <v>0.020263</v>
+        <v>0.019766</v>
       </c>
       <c r="E3" t="n">
-        <v>0.109771</v>
+        <v>0.106572</v>
       </c>
       <c r="F3" t="n">
-        <v>0.054537</v>
+        <v>0.05295</v>
       </c>
       <c r="G3" t="n">
-        <v>0.370035</v>
+        <v>0.337393</v>
       </c>
       <c r="H3" t="n">
-        <v>0.592711</v>
+        <v>0.593262</v>
       </c>
     </row>
     <row r="4">
@@ -527,19 +527,19 @@
         <v>453</v>
       </c>
       <c r="D4" t="n">
-        <v>0.022021</v>
+        <v>0.021499</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1193</v>
+        <v>0.115914</v>
       </c>
       <c r="F4" t="n">
-        <v>0.059271</v>
+        <v>0.057592</v>
       </c>
       <c r="G4" t="n">
-        <v>0.402157</v>
+        <v>0.366969</v>
       </c>
       <c r="H4" t="n">
-        <v>0.644163</v>
+        <v>0.645267</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.001758</v>
+        <v>0.001733</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009528999999999999</v>
+        <v>0.009342</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004734</v>
+        <v>0.004642</v>
       </c>
       <c r="G5" t="n">
-        <v>0.032122</v>
+        <v>0.029576</v>
       </c>
       <c r="H5" t="n">
-        <v>0.051452</v>
+        <v>0.052005</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/distribution_stats.xlsx
+++ b/vignettes/vignette-2/distribution_stats.xlsx
@@ -465,25 +465,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>789</v>
+        <v>726</v>
       </c>
       <c r="C2" t="n">
-        <v>453</v>
+        <v>430</v>
       </c>
       <c r="D2" t="n">
-        <v>0.024278</v>
+        <v>0.028017</v>
       </c>
       <c r="E2" t="n">
-        <v>0.180225</v>
+        <v>0.180364</v>
       </c>
       <c r="F2" t="n">
-        <v>0.067604</v>
+        <v>0.07244399999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>0.766636</v>
+        <v>0.766024</v>
       </c>
       <c r="H2" t="n">
-        <v>0.864212</v>
+        <v>0.865683</v>
       </c>
     </row>
     <row r="3">
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>789</v>
+        <v>726</v>
       </c>
       <c r="C3" t="n">
-        <v>453</v>
+        <v>430</v>
       </c>
       <c r="D3" t="n">
-        <v>0.019766</v>
+        <v>0.020955</v>
       </c>
       <c r="E3" t="n">
-        <v>0.106572</v>
+        <v>0.105789</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05295</v>
+        <v>0.056059</v>
       </c>
       <c r="G3" t="n">
-        <v>0.337393</v>
+        <v>0.337718</v>
       </c>
       <c r="H3" t="n">
-        <v>0.593262</v>
+        <v>0.525852</v>
       </c>
     </row>
     <row r="4">
@@ -521,25 +521,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>789</v>
+        <v>726</v>
       </c>
       <c r="C4" t="n">
-        <v>453</v>
+        <v>430</v>
       </c>
       <c r="D4" t="n">
-        <v>0.021499</v>
+        <v>0.02275</v>
       </c>
       <c r="E4" t="n">
-        <v>0.115914</v>
+        <v>0.114848</v>
       </c>
       <c r="F4" t="n">
-        <v>0.057592</v>
+        <v>0.06086</v>
       </c>
       <c r="G4" t="n">
-        <v>0.366969</v>
+        <v>0.366637</v>
       </c>
       <c r="H4" t="n">
-        <v>0.645267</v>
+        <v>0.570881</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.001733</v>
+        <v>0.001795</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009342</v>
+        <v>0.009058999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004642</v>
+        <v>0.004801</v>
       </c>
       <c r="G5" t="n">
-        <v>0.029576</v>
+        <v>0.028919</v>
       </c>
       <c r="H5" t="n">
-        <v>0.052005</v>
+        <v>0.045029</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/distribution_stats.xlsx
+++ b/vignettes/vignette-2/distribution_stats.xlsx
@@ -499,19 +499,19 @@
         <v>430</v>
       </c>
       <c r="D3" t="n">
-        <v>0.020955</v>
+        <v>0.020961</v>
       </c>
       <c r="E3" t="n">
-        <v>0.105789</v>
+        <v>0.105824</v>
       </c>
       <c r="F3" t="n">
-        <v>0.056059</v>
+        <v>0.05608</v>
       </c>
       <c r="G3" t="n">
-        <v>0.337718</v>
+        <v>0.337412</v>
       </c>
       <c r="H3" t="n">
-        <v>0.525852</v>
+        <v>0.526157</v>
       </c>
     </row>
     <row r="4">
@@ -527,19 +527,19 @@
         <v>430</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02275</v>
+        <v>0.022754</v>
       </c>
       <c r="E4" t="n">
-        <v>0.114848</v>
+        <v>0.114876</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06086</v>
+        <v>0.060877</v>
       </c>
       <c r="G4" t="n">
-        <v>0.366637</v>
+        <v>0.366273</v>
       </c>
       <c r="H4" t="n">
-        <v>0.570881</v>
+        <v>0.571163</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.001795</v>
+        <v>0.001793</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009058999999999999</v>
+        <v>0.009051999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004801</v>
+        <v>0.004797</v>
       </c>
       <c r="G5" t="n">
-        <v>0.028919</v>
+        <v>0.028861</v>
       </c>
       <c r="H5" t="n">
-        <v>0.045029</v>
+        <v>0.045006</v>
       </c>
     </row>
   </sheetData>
